--- a/data/trans_orig/IP09C_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP09C_R-Edad-trans_orig.xlsx
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>535</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4708</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>9236</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4294</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1445,12 +1445,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1535</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1495,12 +1495,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>10442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,21%</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>4567</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14955</t>
+          <t>14797</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>26206</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>49,73%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7381</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10007</t>
+          <t>10054</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,12 +2353,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2388,12 +2388,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7738</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2403,12 +2403,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7762</t>
+          <t>7596</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8157</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5601</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13528</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6484</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,92%</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3163,12 +3163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>8607</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,7 +3772,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1591</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,72%</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10759</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>44,24%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>6540</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4192</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -4477,12 +4477,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4492,12 +4492,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4512,12 +4512,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4625,12 +4625,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4718,12 +4718,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -4816,12 +4816,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4851,12 +4851,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4866,12 +4866,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4929,12 +4929,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4167</t>
+          <t>4732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>8635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>9800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16404</t>
+          <t>16376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13984</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17976</t>
+          <t>17726</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28913</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,23%</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3091</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11325</t>
+          <t>10740</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6347</t>
+          <t>6624</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9546</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13836</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1373</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7386</t>
+          <t>7834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>17164</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6766,12 +6766,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11631</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21849</t>
+          <t>21744</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>23156</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36201</t>
+          <t>36616</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>57,15%</t>
         </is>
       </c>
     </row>
@@ -6899,12 +6899,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>750</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6463</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7062,12 +7062,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,34%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12798</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -7320,12 +7320,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9333</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7586,7 +7586,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -7659,12 +7659,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>11365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7674,12 +7674,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4963</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -8228,12 +8228,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4648</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>17339</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8459,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5027</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -8567,12 +8567,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8602,12 +8602,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>542</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8637,12 +8637,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -8685,7 +8685,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8715,12 +8715,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8750,12 +8750,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12196</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -8793,12 +8793,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8863,12 +8863,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3223</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8941,12 +8941,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1446</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9206,12 +9206,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9284,12 +9284,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -9362,12 +9362,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9397,12 +9397,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -9475,12 +9475,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9490,12 +9490,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9545,12 +9545,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>63055</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -9588,12 +9588,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9716,12 +9716,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9736,12 +9736,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9786,12 +9786,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -9814,12 +9814,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10346,12 +10346,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>679</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10361,12 +10361,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10464,7 +10464,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10522,7 +10522,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10577,7 +10577,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10592,7 +10592,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -10615,12 +10615,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6029</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10630,12 +10630,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10650,12 +10650,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8579</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10665,12 +10665,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10685,12 +10685,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>5924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10700,12 +10700,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1711</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>33,69%</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3246</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4207</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11009,7 +11009,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>5692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11039,12 +11039,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -11184,12 +11184,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>440</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3873</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11199,12 +11199,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8320</t>
+          <t>8628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11234,12 +11234,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11254,12 +11254,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>10606</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -11302,7 +11302,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>4696</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11367,12 +11367,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>898</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -11445,12 +11445,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11460,12 +11460,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5477</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -11523,12 +11523,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11538,12 +11538,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11573,12 +11573,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -11636,12 +11636,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -11749,12 +11749,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>572</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5368</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11764,12 +11764,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10489</t>
+          <t>10469</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11882,7 +11882,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12097,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3743</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12127,7 +12127,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,19%</t>
         </is>
       </c>
     </row>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3726</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -12544,12 +12544,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5287</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12559,12 +12559,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>50,22%</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3323</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12727,12 +12727,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>472</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12742,12 +12742,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -13000,12 +13000,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13015,12 +13015,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5076</t>
+          <t>5178</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13050,12 +13050,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8932</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13085,12 +13085,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -13231,7 +13231,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>717</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13311,12 +13311,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -13339,12 +13339,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13354,12 +13354,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5750</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13389,12 +13389,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10957</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13424,12 +13424,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>54,67%</t>
         </is>
       </c>
     </row>
@@ -13487,12 +13487,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13522,12 +13522,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>38,83%</t>
         </is>
       </c>
     </row>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4286</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13585,7 +13585,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -13908,12 +13908,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13923,12 +13923,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13958,12 +13958,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13993,12 +13993,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14036,12 +14036,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14091,12 +14091,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -14134,12 +14134,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14149,12 +14149,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14169,12 +14169,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14184,12 +14184,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14219,12 +14219,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -14247,12 +14247,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14262,12 +14262,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14282,12 +14282,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14297,12 +14297,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14332,12 +14332,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -14360,12 +14360,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14375,12 +14375,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14395,12 +14395,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14410,12 +14410,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14430,12 +14430,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14445,12 +14445,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -14473,12 +14473,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14488,12 +14488,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14508,12 +14508,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14543,12 +14543,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14636,12 +14636,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14656,12 +14656,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14671,12 +14671,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
